--- a/List_Microsoft_Excel.xlsx
+++ b/List_Microsoft_Excel.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="33">
   <si>
     <t>ППП</t>
   </si>
@@ -123,52 +123,25 @@
     <t>%</t>
   </si>
   <si>
-    <t>CaOсв</t>
-  </si>
-  <si>
-    <t>Na2Oэкв</t>
-  </si>
-  <si>
-    <t>Тонкость по Блейну, см2/г</t>
-  </si>
-  <si>
-    <t>Тонкость сита 45мкм, %</t>
-  </si>
-  <si>
     <t>Тонкость сита 80мкм, %</t>
   </si>
   <si>
     <t>Тонкость сита 90мкм, %</t>
   </si>
   <si>
-    <t>РИО, мм</t>
-  </si>
-  <si>
     <t>Удельный вес, г/см3</t>
   </si>
   <si>
-    <t>Начало схватывания, мин</t>
-  </si>
-  <si>
-    <t>Конец схватывания, мин</t>
-  </si>
-  <si>
-    <t>Прочность 2 сут, МПа</t>
+    <t>Начало, мин.</t>
   </si>
   <si>
     <t>Прочность 3 сут, МПа</t>
   </si>
   <si>
-    <t>Прочность 28 сут, МПа</t>
-  </si>
-  <si>
     <t>Активность радионуклидов, Бк/кг</t>
   </si>
   <si>
-    <t>Клинкер, %</t>
-  </si>
-  <si>
-    <t>Известняк, %</t>
+    <t>Клинкер</t>
   </si>
   <si>
     <t>Прочность на изгиб 2 сут, МПа</t>
@@ -177,61 +150,7 @@
     <t>Прочность на изгиб 28 сут, МПа</t>
   </si>
   <si>
-    <t>Прочность на сжатие 2 сут, МПа</t>
-  </si>
-  <si>
-    <t>Прочность на сжатие 28 сут, МПа</t>
-  </si>
-  <si>
-    <t>Нормальная густота, %</t>
-  </si>
-  <si>
-    <t>Равномерность изменения объёма, мм</t>
-  </si>
-  <si>
-    <t>Тонкость помола R32, %</t>
-  </si>
-  <si>
-    <t>Блейн, см2/г</t>
-  </si>
-  <si>
-    <t>ППП, %</t>
-  </si>
-  <si>
-    <t>Нерастворимый остаток, %</t>
-  </si>
-  <si>
-    <t>SiO2, %</t>
-  </si>
-  <si>
-    <t>Al2O3, %</t>
-  </si>
-  <si>
-    <t>Fe2O3, %</t>
-  </si>
-  <si>
-    <t>CaO, %</t>
-  </si>
-  <si>
-    <t>MgO, %</t>
-  </si>
-  <si>
-    <t>SO3, %</t>
-  </si>
-  <si>
-    <t>K2O, %</t>
-  </si>
-  <si>
-    <t>Na2O, %</t>
-  </si>
-  <si>
-    <t>Cl-, %</t>
-  </si>
-  <si>
-    <t>CaOсв, %</t>
-  </si>
-  <si>
-    <t>Na2O экв, %</t>
+    <t>Cl-</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1418,7 @@
     <col min="15" max="16384" width="9.14285714285714" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:23">
+    <row r="1" spans="1:23">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14514,49 +14433,49 @@
         <v>10</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
       </c>
       <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" t="s">
         <v>25</v>
       </c>
-      <c r="M1" t="s">
+      <c r="R1" t="s">
         <v>26</v>
       </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" t="s">
         <v>27</v>
       </c>
-      <c r="O1" t="s">
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
         <v>28</v>
-      </c>
-      <c r="P1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T1" t="s">
-        <v>33</v>
-      </c>
-      <c r="U1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -22055,79 +21974,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" t="s">
+        <v>8</v>
+      </c>
+      <c r="W1" t="s">
         <v>32</v>
       </c>
-      <c r="J1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>51</v>
-      </c>
-      <c r="R1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V1" t="s">
-        <v>56</v>
-      </c>
-      <c r="W1" t="s">
-        <v>57</v>
-      </c>
       <c r="X1" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="Y1" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:25">
